--- a/results/strict_classifier results/BMW_2014_strict_classified.xlsx
+++ b/results/strict_classifier results/BMW_2014_strict_classified.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c5b0ba968cd3026a/Documents/thesis-greenwashing/results/strict_classifier results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_28518FE7028CD92D7197CB7523101254AD0D679F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49D9008C-AA2D-45B3-BAFE-981C8F69DD47}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_28518FE7028CD92D7197CB7523101254AD0D679F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B6BFD2-6E44-4088-AD4C-BECE7C135838}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,6 +418,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -709,6 +713,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1462,6 +1467,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
